--- a/analysis/coding_worksheets/決策群組_#201.xlsx
+++ b/analysis/coding_worksheets/決策群組_#201.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,145 +451,150 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>from</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S_Amy_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>S_Sally_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>S_Nancy_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_HR2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Ops2</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>U_Amy_Mkt2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR1</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_HR2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Ops2</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>U_Sally_Mkt2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_HR2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Ops2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>U_Nancy_Mkt2</t>
         </is>
@@ -618,17 +623,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>我選 Sally</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -705,6 +712,9 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,17 +741,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>我選 Nancy</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -818,6 +830,9 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,17 +859,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>我選 Sally</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -931,6 +948,9 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,17 +977,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>我想先剃除掉Nancy 就我個人手邊的資料來說 我注意到他是個完全不會表揚他人功勞的人 這樣的主管很難建立起團隊的向心力 我認為他不適任 是否先淘汰他呢</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1044,6 +1066,9 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1070,17 +1095,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>因為現階段公司的障礙有一部份是內部協調有問題、還有各部門的策略不一致，所以我覺得要選一個有領導力，可以讓其他員工信服的人來作為這個關鍵的領導角色。我看到有員工說Sally會利用組織政治為自己謀利，感覺同事們不太會喜歡這樣的人作為領導者。</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1157,6 +1184,9 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1183,10 +1213,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>我的機密資料中顯示
 Amy員工抱怨她很冷漠疏遠，雖重視細節，完成公司課程，就是中規中矩
@@ -1194,9 +1229,6 @@
 Nancy不會表揚他人的貢獻，這跟財務長需要的特質不同，員工都會需要成就感的</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1273,6 +1305,9 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1299,18 +1334,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>我建議待會大家發言時要提出自己看到個別候選人最大的缺點及優點 方便大家討論
 我認為sally會使用組織政治，我讓為完全不該選擇他。我剛剛說Nancy不會表揚員工，就我而言是個可以接受的缺點，Amy我的資料是顯示他很重視細節，而Nancy的優點還有一個是他很嚴格但非常公平，這對於需要平均分配資源的財務長職位，我認為很合適。綜上，我建議撇除掉sally再來討論，各位覺得呢</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1387,6 +1424,9 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1413,19 +1453,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>我同意可以撇除Sally，
 我想改成選擇 Amy ，原因是，我這邊的資料顯示他在擔任公司爭議解決委員會時有良好的表現，很適合在這種時期（決策停滯、大家有協調上的問題）作為領導的角色。然後我這邊的資料顯示關於 Amy 比較負面的內容只有：不是一個鼓舞人心的演講者。我覺得相較另外兩位的負面內容（Sally為自己牟利、Nancy不記得表揚他人貢獻）可能相對輕微一點。
 不過 Nancy 的優點有完成公司提供的領導課程、以及在內部審計實務方面發表大量文章。大家也可以考慮進去。</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1502,6 +1544,9 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,17 +1573,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>三位的經驗都很豐富，經過大家說明，我認為可以選Amy。Sally為自己牟利(他是敵對公司的財務副總裁或許有些爭議)、Nancy不記得表揚他人貢獻，都不是好的財務長應有的特質。我這邊資料顯示Amy，重視細節，也完成公司的培訓，遵守公司規定，或許是不錯的人選。</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1615,6 +1662,9 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1641,10 +1691,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AI_ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>assistant</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>目前討論整理如下：
 - 有成員提到傾向先剃除 Nancy，原因是其不會表揚他人貢獻，認為這會影響團隊向心力，也不符合財務長所需特質。不過也有觀點認為這缺點可接受，並指出其公平、嚴格，有利於資源分配。
@@ -1653,9 +1708,6 @@
 - 綜合目前意見，傾向剃除 Sally，討論焦點逐漸集中於 Amy 與 Nancy。</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1732,6 +1784,9 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1758,17 +1813,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1845,6 +1902,9 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1871,17 +1931,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -1958,6 +2020,9 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1984,17 +2049,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
@@ -2071,6 +2138,9 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2097,17 +2167,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -2184,6 +2256,9 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2210,17 +2285,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -2297,6 +2374,9 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2323,17 +2403,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>需要再討論</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2410,6 +2492,9 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2436,17 +2521,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>所以大家都選 Amy嗎？</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2523,6 +2610,9 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2549,17 +2639,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>選Amy</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2636,6 +2728,9 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2662,17 +2757,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>我也是</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -2749,6 +2846,9 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2775,17 +2875,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>達成共識</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -2862,6 +2964,9 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2888,17 +2993,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -2975,6 +3082,9 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3001,17 +3111,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -3088,6 +3200,9 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3114,17 +3229,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>已有共識</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -3201,6 +3318,9 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3227,17 +3347,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>人資長</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>我們最終選擇 Amy</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
@@ -3314,6 +3436,9 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3340,17 +3465,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>行銷長</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>我們最終選擇 Amy</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
@@ -3427,6 +3554,9 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3453,17 +3583,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>營運長</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>我們最終選擇 Amy</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -3540,6 +3672,9 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0</v>
       </c>
     </row>
